--- a/cl_st1_ph3_ednalvo/avaliacao_composicoes/comparacao_de_avaliadores.xlsx
+++ b/cl_st1_ph3_ednalvo/avaliacao_composicoes/comparacao_de_avaliadores.xlsx
@@ -521,7 +521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>32610_human_low</t>
+          <t>32610_humano_menores_notas</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -591,7 +591,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>32674_human_low</t>
+          <t>32674_humano_menores_notas</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -661,7 +661,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>32714_human_low</t>
+          <t>32714_humano_menores_notas</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -731,7 +731,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>32733_human_low</t>
+          <t>32733_humano_menores_notas</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -801,7 +801,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>32749_human_low</t>
+          <t>32749_humano_menores_notas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -871,7 +871,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>32755_human_low</t>
+          <t>32755_humano_menores_notas</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -941,7 +941,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>32757_human_high</t>
+          <t>32757_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1011,7 +1011,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>32782_human_low</t>
+          <t>32782_humano_menores_notas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1081,7 +1081,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>32792_human_low</t>
+          <t>32792_humano_menores_notas</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1151,7 +1151,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>32860_human_low</t>
+          <t>32860_humano_menores_notas</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1221,7 +1221,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>32875_human_high</t>
+          <t>32875_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1291,7 +1291,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>33083_human_high</t>
+          <t>33083_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1361,7 +1361,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>33167_human_low</t>
+          <t>33167_humano_menores_notas</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1431,7 +1431,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>33228_human_high</t>
+          <t>33228_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1501,7 +1501,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>33310_human_low</t>
+          <t>33310_humano_menores_notas</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1571,7 +1571,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>33360_human_low</t>
+          <t>33360_humano_menores_notas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1641,7 +1641,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>33383_human_high</t>
+          <t>33383_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1711,7 +1711,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>33436_human_low</t>
+          <t>33436_humano_menores_notas</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1781,7 +1781,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>33465_human_low</t>
+          <t>33465_humano_menores_notas</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1851,7 +1851,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>33497_human_low</t>
+          <t>33497_humano_menores_notas</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1921,7 +1921,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>33645_human_low</t>
+          <t>33645_humano_menores_notas</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1991,7 +1991,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>33669_human_high</t>
+          <t>33669_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2061,7 +2061,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>33787_human_low</t>
+          <t>33787_humano_menores_notas</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2131,7 +2131,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>33789_human_low</t>
+          <t>33789_humano_menores_notas</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2201,7 +2201,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>33849_human_high</t>
+          <t>33849_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2271,7 +2271,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>33856_human_low</t>
+          <t>33856_humano_menores_notas</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2341,7 +2341,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>33862_human_low</t>
+          <t>33862_humano_menores_notas</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2411,7 +2411,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>33871_human_low</t>
+          <t>33871_humano_menores_notas</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2481,7 +2481,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>33879_human_high</t>
+          <t>33879_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2551,7 +2551,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>33890_human_high</t>
+          <t>33890_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2621,7 +2621,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>33895_human_high</t>
+          <t>33895_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2691,7 +2691,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>33914_human_high</t>
+          <t>33914_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2761,7 +2761,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>33927_human_high</t>
+          <t>33927_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -2831,7 +2831,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>33948_human_low</t>
+          <t>33948_humano_menores_notas</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -2901,7 +2901,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>33964_human_low</t>
+          <t>33964_humano_menores_notas</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -2971,7 +2971,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>33975_human_high</t>
+          <t>33975_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -3041,7 +3041,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>33978_human_high</t>
+          <t>33978_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -3111,7 +3111,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>33991_human_high</t>
+          <t>33991_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -3181,7 +3181,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>33999_human_high</t>
+          <t>33999_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -3251,7 +3251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>34009_human_low</t>
+          <t>34009_humano_menores_notas</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -3321,7 +3321,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>34025_human_low</t>
+          <t>34025_humano_menores_notas</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -3391,7 +3391,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>34032_human_high</t>
+          <t>34032_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -3461,7 +3461,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>34046_human_low</t>
+          <t>34046_humano_menores_notas</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -3531,7 +3531,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>34050_human_high</t>
+          <t>34050_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -3601,7 +3601,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>34084_human_high</t>
+          <t>34084_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -3671,7 +3671,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>34086_human_high</t>
+          <t>34086_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -3741,7 +3741,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>34096_human_high</t>
+          <t>34096_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -3811,7 +3811,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>34116_human_high</t>
+          <t>34116_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -3881,7 +3881,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>34148_human_high</t>
+          <t>34148_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -3951,7 +3951,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>34175_human_high</t>
+          <t>34175_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -4021,7 +4021,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>34185_human_low</t>
+          <t>34185_humano_menores_notas</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -4091,7 +4091,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>34210_human_low</t>
+          <t>34210_humano_menores_notas</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -4161,7 +4161,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>34236_human_low</t>
+          <t>34236_humano_menores_notas</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -4231,7 +4231,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>34251_human_low</t>
+          <t>34251_humano_menores_notas</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -4301,7 +4301,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>34273_human_low</t>
+          <t>34273_humano_menores_notas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -4371,7 +4371,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>34277_human_high</t>
+          <t>34277_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -4441,7 +4441,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>34281_human_high</t>
+          <t>34281_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -4511,7 +4511,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>34306_human_high</t>
+          <t>34306_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -4581,7 +4581,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>34308_human_low</t>
+          <t>34308_humano_menores_notas</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -4651,7 +4651,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>34353_human_high</t>
+          <t>34353_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -4721,7 +4721,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>34356_human_low</t>
+          <t>34356_humano_menores_notas</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -4791,7 +4791,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>34362_human_low</t>
+          <t>34362_humano_menores_notas</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -4861,7 +4861,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>34381_human_high</t>
+          <t>34381_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -4931,7 +4931,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>34419_human_high</t>
+          <t>34419_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -5001,7 +5001,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>34461_human_high</t>
+          <t>34461_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -5071,7 +5071,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>34511_human_high</t>
+          <t>34511_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -5141,7 +5141,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>34537_human_low</t>
+          <t>34537_humano_menores_notas</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -5211,7 +5211,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>34613_human_low</t>
+          <t>34613_humano_menores_notas</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -5281,7 +5281,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>34616_human_low</t>
+          <t>34616_humano_menores_notas</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -5351,7 +5351,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>34618_human_low</t>
+          <t>34618_humano_menores_notas</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -5421,7 +5421,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>34637_human_low</t>
+          <t>34637_humano_menores_notas</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -5491,7 +5491,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>34638_human_low</t>
+          <t>34638_humano_menores_notas</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -5561,7 +5561,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>34641_human_high</t>
+          <t>34641_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -5631,7 +5631,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>34642_human_low</t>
+          <t>34642_humano_menores_notas</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -5701,7 +5701,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>34648_human_high</t>
+          <t>34648_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -5771,7 +5771,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>34652_human_high</t>
+          <t>34652_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -5841,7 +5841,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>34675_human_high</t>
+          <t>34675_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -5911,7 +5911,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>34698_human_high</t>
+          <t>34698_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -5981,7 +5981,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>34714_human_low</t>
+          <t>34714_humano_menores_notas</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -6051,7 +6051,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>34717_human_high</t>
+          <t>34717_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -6121,7 +6121,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>34726_human_high</t>
+          <t>34726_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -6191,7 +6191,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>34743_human_low</t>
+          <t>34743_humano_menores_notas</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -6261,7 +6261,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>34754_human_high</t>
+          <t>34754_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -6331,7 +6331,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>34802_human_high</t>
+          <t>34802_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -6401,7 +6401,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>34807_human_low</t>
+          <t>34807_humano_menores_notas</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -6471,7 +6471,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>34811_human_high</t>
+          <t>34811_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -6541,7 +6541,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>34813_human_high</t>
+          <t>34813_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -6611,7 +6611,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>34823_human_low</t>
+          <t>34823_humano_menores_notas</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -6681,7 +6681,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>34832_human_high</t>
+          <t>34832_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -6751,7 +6751,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>34841_human_high</t>
+          <t>34841_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -6821,7 +6821,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>34844_human_high</t>
+          <t>34844_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -6891,7 +6891,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>34875_human_high</t>
+          <t>34875_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -6961,7 +6961,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>34895_human_low</t>
+          <t>34895_humano_menores_notas</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -7031,7 +7031,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>34901_human_high</t>
+          <t>34901_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -7101,7 +7101,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>34967_human_high</t>
+          <t>34967_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -7171,7 +7171,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>34971_human_low</t>
+          <t>34971_humano_menores_notas</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -7241,7 +7241,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>34994_human_high</t>
+          <t>34994_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -7311,7 +7311,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>35019_human_low</t>
+          <t>35019_humano_menores_notas</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -7381,7 +7381,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>35028_human_low</t>
+          <t>35028_humano_menores_notas</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -7451,7 +7451,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>35053_human_high</t>
+          <t>35053_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -7521,7 +7521,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>35056_human_low</t>
+          <t>35056_humano_menores_notas</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -7591,7 +7591,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>35071_human_low</t>
+          <t>35071_humano_menores_notas</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -7661,7 +7661,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>35072_human_low</t>
+          <t>35072_humano_menores_notas</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -7731,7 +7731,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>35077_human_high</t>
+          <t>35077_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -7801,7 +7801,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>35100_human_high</t>
+          <t>35100_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -7871,7 +7871,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>35121_human_high</t>
+          <t>35121_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -7941,7 +7941,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>35125_human_high</t>
+          <t>35125_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -8011,7 +8011,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>35126_human_high</t>
+          <t>35126_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -8081,7 +8081,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>35131_human_low</t>
+          <t>35131_humano_menores_notas</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -8151,7 +8151,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>35134_human_high</t>
+          <t>35134_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -8221,7 +8221,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>35136_human_low</t>
+          <t>35136_humano_menores_notas</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -8291,7 +8291,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>35163_human_low</t>
+          <t>35163_humano_menores_notas</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -8361,7 +8361,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>35173_human_low</t>
+          <t>35173_humano_menores_notas</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -8431,7 +8431,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>35198_human_low</t>
+          <t>35198_humano_menores_notas</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -8501,7 +8501,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>35214_human_low</t>
+          <t>35214_humano_menores_notas</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -8571,7 +8571,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>35217_human_low</t>
+          <t>35217_humano_menores_notas</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -8641,7 +8641,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>35220_human_low</t>
+          <t>35220_humano_menores_notas</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -8711,7 +8711,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>35228_human_low</t>
+          <t>35228_humano_menores_notas</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -8781,7 +8781,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>35240_human_high</t>
+          <t>35240_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -8851,7 +8851,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>35247_human_high</t>
+          <t>35247_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -8921,7 +8921,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>35278_human_low</t>
+          <t>35278_humano_menores_notas</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -8991,7 +8991,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>35291_human_low</t>
+          <t>35291_humano_menores_notas</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -9061,7 +9061,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>35378_human_high</t>
+          <t>35378_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -9131,7 +9131,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>35400_human_high</t>
+          <t>35400_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -9201,7 +9201,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>35451_human_high</t>
+          <t>35451_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -9271,7 +9271,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>35457_human_low</t>
+          <t>35457_humano_menores_notas</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -9341,7 +9341,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>35464_human_high</t>
+          <t>35464_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -9411,7 +9411,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>35465_human_low</t>
+          <t>35465_humano_menores_notas</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -9481,7 +9481,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>35482_human_high</t>
+          <t>35482_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -9551,7 +9551,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>35485_human_low</t>
+          <t>35485_humano_menores_notas</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -9621,7 +9621,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>35496_human_high</t>
+          <t>35496_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -9691,7 +9691,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>35497_human_high</t>
+          <t>35497_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -9761,7 +9761,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>35542_human_high</t>
+          <t>35542_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -9831,7 +9831,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>35549_human_low</t>
+          <t>35549_humano_menores_notas</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -9901,7 +9901,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>35577_human_low</t>
+          <t>35577_humano_menores_notas</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -9971,7 +9971,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>35633_human_low</t>
+          <t>35633_humano_menores_notas</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -10041,7 +10041,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>35647_human_high</t>
+          <t>35647_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -10111,7 +10111,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>35661_human_low</t>
+          <t>35661_humano_menores_notas</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -10181,7 +10181,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>35733_human_high</t>
+          <t>35733_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -10251,7 +10251,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>35734_human_high</t>
+          <t>35734_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -10321,7 +10321,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>35750_human_high</t>
+          <t>35750_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -10391,7 +10391,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>35763_human_high</t>
+          <t>35763_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E143" t="n">
@@ -10461,7 +10461,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>35789_human_high</t>
+          <t>35789_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -10531,7 +10531,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>35819_human_high</t>
+          <t>35819_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -10601,7 +10601,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>35820_human_low</t>
+          <t>35820_humano_menores_notas</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -10671,7 +10671,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>35852_human_low</t>
+          <t>35852_humano_menores_notas</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -10741,7 +10741,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>35865_human_high</t>
+          <t>35865_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -10811,7 +10811,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>35867_human_high</t>
+          <t>35867_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E149" t="n">
@@ -10881,7 +10881,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>35892_human_high</t>
+          <t>35892_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -10951,7 +10951,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>35906_human_low</t>
+          <t>35906_humano_menores_notas</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E151" t="n">
@@ -11021,7 +11021,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>35911_human_low</t>
+          <t>35911_humano_menores_notas</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -11091,7 +11091,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>35928_human_high</t>
+          <t>35928_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -11161,7 +11161,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>35934_human_high</t>
+          <t>35934_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -11231,7 +11231,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>35937_human_low</t>
+          <t>35937_humano_menores_notas</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -11301,7 +11301,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>35979_human_low</t>
+          <t>35979_humano_menores_notas</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -11371,7 +11371,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>35986_human_low</t>
+          <t>35986_humano_menores_notas</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -11441,7 +11441,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>35994_human_high</t>
+          <t>35994_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -11511,7 +11511,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>36000_human_low</t>
+          <t>36000_humano_menores_notas</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -11581,7 +11581,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>36006_human_high</t>
+          <t>36006_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11596,7 +11596,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -11651,7 +11651,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>36030_human_high</t>
+          <t>36030_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -11721,7 +11721,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>36064_human_high</t>
+          <t>36064_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -11791,7 +11791,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>36068_human_high</t>
+          <t>36068_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -11861,7 +11861,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>36074_human_high</t>
+          <t>36074_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -11931,7 +11931,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>36079_human_low</t>
+          <t>36079_humano_menores_notas</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11946,7 +11946,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E165" t="n">
@@ -12001,7 +12001,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>36085_human_low</t>
+          <t>36085_humano_menores_notas</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -12071,7 +12071,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>36090_human_high</t>
+          <t>36090_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -12141,7 +12141,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>36095_human_low</t>
+          <t>36095_humano_menores_notas</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -12211,7 +12211,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>36137_human_low</t>
+          <t>36137_humano_menores_notas</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -12226,7 +12226,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -12281,7 +12281,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>36140_human_low</t>
+          <t>36140_humano_menores_notas</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -12351,7 +12351,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>36163_human_high</t>
+          <t>36163_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -12421,7 +12421,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>36172_human_low</t>
+          <t>36172_humano_menores_notas</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -12436,7 +12436,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -12491,7 +12491,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>36181_human_low</t>
+          <t>36181_humano_menores_notas</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -12561,7 +12561,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>36188_human_low</t>
+          <t>36188_humano_menores_notas</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -12631,7 +12631,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>36214_human_high</t>
+          <t>36214_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -12646,7 +12646,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -12701,7 +12701,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>36225_human_low</t>
+          <t>36225_humano_menores_notas</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -12771,7 +12771,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>36237_human_high</t>
+          <t>36237_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -12841,7 +12841,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>36238_human_low</t>
+          <t>36238_humano_menores_notas</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -12911,7 +12911,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>36245_human_high</t>
+          <t>36245_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -12981,7 +12981,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>36248_human_low</t>
+          <t>36248_humano_menores_notas</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -13051,7 +13051,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>36260_human_high</t>
+          <t>36260_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -13121,7 +13121,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>36261_human_high</t>
+          <t>36261_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -13191,7 +13191,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>36278_human_low</t>
+          <t>36278_humano_menores_notas</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -13206,7 +13206,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -13261,7 +13261,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>36280_human_high</t>
+          <t>36280_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -13276,7 +13276,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -13331,7 +13331,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>36295_human_low</t>
+          <t>36295_humano_menores_notas</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -13401,7 +13401,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>36307_human_low</t>
+          <t>36307_humano_menores_notas</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -13471,7 +13471,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>36330_human_high</t>
+          <t>36330_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -13541,7 +13541,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>36341_human_low</t>
+          <t>36341_humano_menores_notas</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -13611,7 +13611,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>36349_human_high</t>
+          <t>36349_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -13681,7 +13681,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>36385_human_high</t>
+          <t>36385_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -13696,7 +13696,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -13751,7 +13751,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>36403_human_high</t>
+          <t>36403_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -13821,7 +13821,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>36415_human_high</t>
+          <t>36415_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -13836,7 +13836,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -13891,7 +13891,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>36430_human_low</t>
+          <t>36430_humano_menores_notas</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -13906,7 +13906,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E193" t="n">
@@ -13961,7 +13961,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>36436_human_high</t>
+          <t>36436_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E194" t="n">
@@ -14031,7 +14031,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>36441_human_high</t>
+          <t>36441_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -14101,7 +14101,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>36442_human_high</t>
+          <t>36442_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -14116,7 +14116,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -14171,7 +14171,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>36471_human_high</t>
+          <t>36471_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -14241,7 +14241,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>36494_human_high</t>
+          <t>36494_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -14256,7 +14256,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -14311,7 +14311,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>36503_human_high</t>
+          <t>36503_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E199" t="n">
@@ -14381,7 +14381,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>36515_human_high</t>
+          <t>36515_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -14451,7 +14451,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>36522_human_low</t>
+          <t>36522_humano_menores_notas</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -14466,7 +14466,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E201" t="n">
@@ -14521,7 +14521,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>36524_human_low</t>
+          <t>36524_humano_menores_notas</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -14591,7 +14591,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>36532_human_high</t>
+          <t>36532_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -14606,7 +14606,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -14661,7 +14661,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>36547_human_low</t>
+          <t>36547_humano_menores_notas</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -14731,7 +14731,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>36551_human_high</t>
+          <t>36551_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -14801,7 +14801,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>36560_human_high</t>
+          <t>36560_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -14871,7 +14871,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>36566_human_high</t>
+          <t>36566_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -14941,7 +14941,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>36577_human_high</t>
+          <t>36577_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -14956,7 +14956,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -15011,7 +15011,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>36578_human_low</t>
+          <t>36578_humano_menores_notas</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -15081,7 +15081,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>36590_human_low</t>
+          <t>36590_humano_menores_notas</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -15151,7 +15151,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>36616_human_low</t>
+          <t>36616_humano_menores_notas</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -15221,7 +15221,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>36626_human_high</t>
+          <t>36626_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -15291,7 +15291,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>36650_human_high</t>
+          <t>36650_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E213" t="n">
@@ -15361,7 +15361,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>36691_human_high</t>
+          <t>36691_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E214" t="n">
@@ -15431,7 +15431,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>36704_human_low</t>
+          <t>36704_humano_menores_notas</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E215" t="n">
@@ -15501,7 +15501,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>36707_human_high</t>
+          <t>36707_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -15516,7 +15516,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E216" t="n">
@@ -15571,7 +15571,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>36721_human_low</t>
+          <t>36721_humano_menores_notas</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E217" t="n">
@@ -15641,7 +15641,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>36727_human_low</t>
+          <t>36727_humano_menores_notas</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -15711,7 +15711,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>36742_human_low</t>
+          <t>36742_humano_menores_notas</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -15781,7 +15781,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>36743_human_high</t>
+          <t>36743_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -15796,7 +15796,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -15851,7 +15851,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>36769_human_high</t>
+          <t>36769_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E221" t="n">
@@ -15921,7 +15921,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>36777_human_high</t>
+          <t>36777_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -15936,7 +15936,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -15991,7 +15991,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>36782_human_high</t>
+          <t>36782_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -16006,7 +16006,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -16061,7 +16061,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>36794_human_high</t>
+          <t>36794_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -16131,7 +16131,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>36797_human_low</t>
+          <t>36797_humano_menores_notas</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E225" t="n">
@@ -16201,7 +16201,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>36822_human_high</t>
+          <t>36822_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -16216,7 +16216,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E226" t="n">
@@ -16271,7 +16271,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>36827_human_low</t>
+          <t>36827_humano_menores_notas</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -16341,7 +16341,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>36845_human_high</t>
+          <t>36845_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -16411,7 +16411,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>36856_human_low</t>
+          <t>36856_humano_menores_notas</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -16426,7 +16426,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -16481,7 +16481,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>36862_human_high</t>
+          <t>36862_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -16496,7 +16496,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -16551,7 +16551,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>36867_human_low</t>
+          <t>36867_humano_menores_notas</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -16566,7 +16566,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -16621,7 +16621,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>36872_human_low</t>
+          <t>36872_humano_menores_notas</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -16691,7 +16691,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>36923_human_high</t>
+          <t>36923_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E233" t="n">
@@ -16761,7 +16761,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>36926_human_high</t>
+          <t>36926_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E234" t="n">
@@ -16831,7 +16831,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>36937_human_high</t>
+          <t>36937_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -16846,7 +16846,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E235" t="n">
@@ -16901,7 +16901,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>36945_human_high</t>
+          <t>36945_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E236" t="n">
@@ -16971,7 +16971,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>36966_human_high</t>
+          <t>36966_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -16986,7 +16986,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E237" t="n">
@@ -17041,7 +17041,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>36973_human_low</t>
+          <t>36973_humano_menores_notas</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -17111,7 +17111,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>36976_human_high</t>
+          <t>36976_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -17126,7 +17126,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E239" t="n">
@@ -17181,7 +17181,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>36988_human_high</t>
+          <t>36988_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E240" t="n">
@@ -17251,7 +17251,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>37010_human_low</t>
+          <t>37010_humano_menores_notas</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E241" t="n">
@@ -17321,7 +17321,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>37015_human_high</t>
+          <t>37015_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -17336,7 +17336,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -17391,7 +17391,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>37034_human_low</t>
+          <t>37034_humano_menores_notas</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -17406,7 +17406,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E243" t="n">
@@ -17461,7 +17461,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>37043_human_low</t>
+          <t>37043_humano_menores_notas</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -17476,7 +17476,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E244" t="n">
@@ -17531,7 +17531,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>37063_human_low</t>
+          <t>37063_humano_menores_notas</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -17546,7 +17546,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E245" t="n">
@@ -17601,7 +17601,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>37078_human_low</t>
+          <t>37078_humano_menores_notas</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -17616,7 +17616,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -17671,7 +17671,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>37094_human_low</t>
+          <t>37094_humano_menores_notas</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -17686,7 +17686,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E247" t="n">
@@ -17741,7 +17741,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>37099_human_low</t>
+          <t>37099_humano_menores_notas</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -17756,7 +17756,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E248" t="n">
@@ -17811,7 +17811,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>37102_human_high</t>
+          <t>37102_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -17826,7 +17826,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E249" t="n">
@@ -17881,7 +17881,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>37126_human_high</t>
+          <t>37126_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -17896,7 +17896,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E250" t="n">
@@ -17951,7 +17951,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>37158_human_low</t>
+          <t>37158_humano_menores_notas</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E251" t="n">
@@ -18021,7 +18021,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>37193_human_high</t>
+          <t>37193_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -18036,7 +18036,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E252" t="n">
@@ -18091,7 +18091,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>37212_human_low</t>
+          <t>37212_humano_menores_notas</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -18106,7 +18106,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E253" t="n">
@@ -18161,7 +18161,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>37224_human_low</t>
+          <t>37224_humano_menores_notas</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -18176,7 +18176,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E254" t="n">
@@ -18231,7 +18231,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>37260_human_low</t>
+          <t>37260_humano_menores_notas</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -18246,7 +18246,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -18301,7 +18301,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>37284_human_high</t>
+          <t>37284_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -18316,7 +18316,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E256" t="n">
@@ -18371,7 +18371,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>37293_human_high</t>
+          <t>37293_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -18386,7 +18386,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E257" t="n">
@@ -18441,7 +18441,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>37321_human_high</t>
+          <t>37321_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -18456,7 +18456,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -18511,7 +18511,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>37345_human_low</t>
+          <t>37345_humano_menores_notas</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -18526,7 +18526,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E259" t="n">
@@ -18581,7 +18581,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>37362_human_high</t>
+          <t>37362_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E260" t="n">
@@ -18651,7 +18651,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>37376_human_high</t>
+          <t>37376_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E261" t="n">
@@ -18721,7 +18721,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>37377_human_low</t>
+          <t>37377_humano_menores_notas</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -18736,7 +18736,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E262" t="n">
@@ -18791,7 +18791,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>37386_human_high</t>
+          <t>37386_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E263" t="n">
@@ -18861,7 +18861,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>37416_human_high</t>
+          <t>37416_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E264" t="n">
@@ -18931,7 +18931,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>37442_human_low</t>
+          <t>37442_humano_menores_notas</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -18946,7 +18946,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E265" t="n">
@@ -19001,7 +19001,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>37480_human_high</t>
+          <t>37480_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E266" t="n">
@@ -19071,7 +19071,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>37489_human_low</t>
+          <t>37489_humano_menores_notas</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -19086,7 +19086,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E267" t="n">
@@ -19141,7 +19141,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>37525_human_high</t>
+          <t>37525_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -19156,7 +19156,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E268" t="n">
@@ -19211,7 +19211,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>37602_human_low</t>
+          <t>37602_humano_menores_notas</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -19226,7 +19226,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E269" t="n">
@@ -19281,7 +19281,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>37605_human_high</t>
+          <t>37605_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -19296,7 +19296,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -19351,7 +19351,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>37612_human_high</t>
+          <t>37612_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E271" t="n">
@@ -19421,7 +19421,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>37655_human_high</t>
+          <t>37655_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -19436,7 +19436,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E272" t="n">
@@ -19491,7 +19491,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>37662_human_high</t>
+          <t>37662_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -19506,7 +19506,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E273" t="n">
@@ -19561,7 +19561,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>37664_human_low</t>
+          <t>37664_humano_menores_notas</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -19576,7 +19576,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E274" t="n">
@@ -19631,7 +19631,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>37677_human_low</t>
+          <t>37677_humano_menores_notas</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E275" t="n">
@@ -19701,7 +19701,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>37681_human_high</t>
+          <t>37681_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -19716,7 +19716,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E276" t="n">
@@ -19771,7 +19771,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>37687_human_high</t>
+          <t>37687_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -19786,7 +19786,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E277" t="n">
@@ -19841,7 +19841,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>37694_human_low</t>
+          <t>37694_humano_menores_notas</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E278" t="n">
@@ -19911,7 +19911,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>37734_human_low</t>
+          <t>37734_humano_menores_notas</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E279" t="n">
@@ -19981,7 +19981,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>37753_human_high</t>
+          <t>37753_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -19996,7 +19996,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E280" t="n">
@@ -20051,7 +20051,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>37754_human_high</t>
+          <t>37754_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E281" t="n">
@@ -20121,7 +20121,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>37783_human_high</t>
+          <t>37783_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E282" t="n">
@@ -20191,7 +20191,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>37801_human_high</t>
+          <t>37801_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -20206,7 +20206,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E283" t="n">
@@ -20261,7 +20261,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>37817_human_high</t>
+          <t>37817_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -20276,7 +20276,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E284" t="n">
@@ -20331,7 +20331,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>37858_human_low</t>
+          <t>37858_humano_menores_notas</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -20346,7 +20346,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E285" t="n">
@@ -20401,7 +20401,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>37922_human_high</t>
+          <t>37922_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -20416,7 +20416,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -20471,7 +20471,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>37924_human_high</t>
+          <t>37924_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -20486,7 +20486,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E287" t="n">
@@ -20541,7 +20541,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>37949_human_low</t>
+          <t>37949_humano_menores_notas</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -20556,7 +20556,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E288" t="n">
@@ -20611,7 +20611,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>37961_human_high</t>
+          <t>37961_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -20626,7 +20626,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E289" t="n">
@@ -20681,7 +20681,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>37994_human_low</t>
+          <t>37994_humano_menores_notas</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -20696,7 +20696,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E290" t="n">
@@ -20751,7 +20751,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>37999_human_low</t>
+          <t>37999_humano_menores_notas</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -20766,7 +20766,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E291" t="n">
@@ -20821,7 +20821,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>38002_human_low</t>
+          <t>38002_humano_menores_notas</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E292" t="n">
@@ -20891,7 +20891,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>38020_human_high</t>
+          <t>38020_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -20906,7 +20906,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E293" t="n">
@@ -20961,7 +20961,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>38036_human_low</t>
+          <t>38036_humano_menores_notas</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -20976,7 +20976,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E294" t="n">
@@ -21031,7 +21031,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>38047_human_high</t>
+          <t>38047_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -21046,7 +21046,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E295" t="n">
@@ -21101,7 +21101,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>38061_human_high</t>
+          <t>38061_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -21116,7 +21116,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E296" t="n">
@@ -21171,7 +21171,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>38080_human_high</t>
+          <t>38080_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -21186,7 +21186,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E297" t="n">
@@ -21241,7 +21241,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>38105_human_high</t>
+          <t>38105_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -21256,7 +21256,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E298" t="n">
@@ -21311,7 +21311,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>38158_human_low</t>
+          <t>38158_humano_menores_notas</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E299" t="n">
@@ -21381,7 +21381,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>38172_human_low</t>
+          <t>38172_humano_menores_notas</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -21396,7 +21396,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E300" t="n">
@@ -21451,7 +21451,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>38193_human_low</t>
+          <t>38193_humano_menores_notas</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -21466,7 +21466,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E301" t="n">
@@ -21521,7 +21521,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>38196_human_low</t>
+          <t>38196_humano_menores_notas</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -21536,7 +21536,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E302" t="n">
@@ -21591,7 +21591,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>38204_human_low</t>
+          <t>38204_humano_menores_notas</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -21606,7 +21606,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E303" t="n">
@@ -21661,7 +21661,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>38226_human_low</t>
+          <t>38226_humano_menores_notas</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -21676,7 +21676,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E304" t="n">
@@ -21731,7 +21731,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>38236_human_high</t>
+          <t>38236_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -21746,7 +21746,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E305" t="n">
@@ -21801,7 +21801,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>38284_human_low</t>
+          <t>38284_humano_menores_notas</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -21816,7 +21816,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E306" t="n">
@@ -21871,7 +21871,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>38310_human_low</t>
+          <t>38310_humano_menores_notas</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -21886,7 +21886,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E307" t="n">
@@ -21941,7 +21941,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>38333_human_high</t>
+          <t>38333_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E308" t="n">
@@ -22011,7 +22011,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>38340_human_low</t>
+          <t>38340_humano_menores_notas</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -22026,7 +22026,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E309" t="n">
@@ -22081,7 +22081,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>38367_human_high</t>
+          <t>38367_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -22096,7 +22096,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E310" t="n">
@@ -22151,7 +22151,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>38392_human_high</t>
+          <t>38392_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -22166,7 +22166,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E311" t="n">
@@ -22221,7 +22221,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>38395_human_low</t>
+          <t>38395_humano_menores_notas</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -22236,7 +22236,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E312" t="n">
@@ -22291,7 +22291,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>38406_human_high</t>
+          <t>38406_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -22306,7 +22306,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E313" t="n">
@@ -22361,7 +22361,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>38437_human_high</t>
+          <t>38437_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -22376,7 +22376,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E314" t="n">
@@ -22431,7 +22431,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>38439_human_low</t>
+          <t>38439_humano_menores_notas</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -22446,7 +22446,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E315" t="n">
@@ -22501,7 +22501,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>38445_human_low</t>
+          <t>38445_humano_menores_notas</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -22516,7 +22516,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E316" t="n">
@@ -22571,7 +22571,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>38451_human_low</t>
+          <t>38451_humano_menores_notas</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -22586,7 +22586,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E317" t="n">
@@ -22641,7 +22641,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>38469_human_low</t>
+          <t>38469_humano_menores_notas</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -22656,7 +22656,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E318" t="n">
@@ -22711,7 +22711,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>38475_human_high</t>
+          <t>38475_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -22726,7 +22726,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E319" t="n">
@@ -22781,7 +22781,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>38493_human_high</t>
+          <t>38493_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -22796,7 +22796,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E320" t="n">
@@ -22851,7 +22851,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>38495_human_low</t>
+          <t>38495_humano_menores_notas</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -22866,7 +22866,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E321" t="n">
@@ -22921,7 +22921,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>38499_human_low</t>
+          <t>38499_humano_menores_notas</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E322" t="n">
@@ -22991,7 +22991,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>38506_human_low</t>
+          <t>38506_humano_menores_notas</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -23006,7 +23006,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E323" t="n">
@@ -23061,7 +23061,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>38536_human_low</t>
+          <t>38536_humano_menores_notas</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -23076,7 +23076,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E324" t="n">
@@ -23131,7 +23131,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>38555_human_low</t>
+          <t>38555_humano_menores_notas</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -23146,7 +23146,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E325" t="n">
@@ -23201,7 +23201,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>38562_human_high</t>
+          <t>38562_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -23216,7 +23216,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E326" t="n">
@@ -23271,7 +23271,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>38584_human_high</t>
+          <t>38584_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -23286,7 +23286,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E327" t="n">
@@ -23341,7 +23341,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>38612_human_high</t>
+          <t>38612_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -23356,7 +23356,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E328" t="n">
@@ -23411,7 +23411,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>38632_human_low</t>
+          <t>38632_humano_menores_notas</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -23426,7 +23426,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E329" t="n">
@@ -23481,7 +23481,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>38637_human_low</t>
+          <t>38637_humano_menores_notas</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -23496,7 +23496,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E330" t="n">
@@ -23551,7 +23551,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>38641_human_high</t>
+          <t>38641_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -23566,7 +23566,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E331" t="n">
@@ -23621,7 +23621,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>38670_human_low</t>
+          <t>38670_humano_menores_notas</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -23636,7 +23636,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E332" t="n">
@@ -23691,7 +23691,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>38672_human_high</t>
+          <t>38672_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -23706,7 +23706,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E333" t="n">
@@ -23761,7 +23761,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>38674_human_low</t>
+          <t>38674_humano_menores_notas</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E334" t="n">
@@ -23831,7 +23831,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>38677_human_low</t>
+          <t>38677_humano_menores_notas</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -23846,7 +23846,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E335" t="n">
@@ -23901,7 +23901,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>38742_human_high</t>
+          <t>38742_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -23916,7 +23916,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E336" t="n">
@@ -23971,7 +23971,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>38764_human_low</t>
+          <t>38764_humano_menores_notas</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -23986,7 +23986,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E337" t="n">
@@ -24041,7 +24041,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>38784_human_high</t>
+          <t>38784_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -24056,7 +24056,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E338" t="n">
@@ -24111,7 +24111,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>38786_human_low</t>
+          <t>38786_humano_menores_notas</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -24126,7 +24126,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E339" t="n">
@@ -24181,7 +24181,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>38794_human_low</t>
+          <t>38794_humano_menores_notas</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E340" t="n">
@@ -24251,7 +24251,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>38845_human_high</t>
+          <t>38845_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -24266,7 +24266,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E341" t="n">
@@ -24321,7 +24321,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>38848_human_high</t>
+          <t>38848_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -24336,7 +24336,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E342" t="n">
@@ -24391,7 +24391,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>38891_human_low</t>
+          <t>38891_humano_menores_notas</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -24406,7 +24406,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E343" t="n">
@@ -24461,7 +24461,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>38917_human_low</t>
+          <t>38917_humano_menores_notas</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -24476,7 +24476,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E344" t="n">
@@ -24531,7 +24531,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>38928_human_low</t>
+          <t>38928_humano_menores_notas</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -24546,7 +24546,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E345" t="n">
@@ -24601,7 +24601,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>38957_human_low</t>
+          <t>38957_humano_menores_notas</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -24616,7 +24616,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E346" t="n">
@@ -24671,7 +24671,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>38958_human_high</t>
+          <t>38958_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -24686,7 +24686,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E347" t="n">
@@ -24741,7 +24741,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>38970_human_low</t>
+          <t>38970_humano_menores_notas</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E348" t="n">
@@ -24811,7 +24811,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>39063_human_low</t>
+          <t>39063_humano_menores_notas</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -24826,7 +24826,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E349" t="n">
@@ -24881,7 +24881,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>39065_human_low</t>
+          <t>39065_humano_menores_notas</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -24896,7 +24896,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E350" t="n">
@@ -24951,7 +24951,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>39108_human_high</t>
+          <t>39108_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -24966,7 +24966,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E351" t="n">
@@ -25021,7 +25021,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>39124_human_low</t>
+          <t>39124_humano_menores_notas</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -25036,7 +25036,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E352" t="n">
@@ -25091,7 +25091,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>39131_human_high</t>
+          <t>39131_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -25106,7 +25106,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E353" t="n">
@@ -25161,7 +25161,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>39164_human_low</t>
+          <t>39164_humano_menores_notas</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -25176,7 +25176,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E354" t="n">
@@ -25231,7 +25231,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>39227_human_high</t>
+          <t>39227_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -25246,7 +25246,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E355" t="n">
@@ -25301,7 +25301,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>39244_human_high</t>
+          <t>39244_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -25316,7 +25316,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E356" t="n">
@@ -25371,7 +25371,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>39298_human_high</t>
+          <t>39298_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -25386,7 +25386,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E357" t="n">
@@ -25441,7 +25441,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>39302_human_low</t>
+          <t>39302_humano_menores_notas</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -25456,7 +25456,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E358" t="n">
@@ -25511,7 +25511,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>39305_human_high</t>
+          <t>39305_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -25526,7 +25526,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E359" t="n">
@@ -25581,7 +25581,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>39349_human_low</t>
+          <t>39349_humano_menores_notas</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -25596,7 +25596,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E360" t="n">
@@ -25651,7 +25651,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>39379_human_low</t>
+          <t>39379_humano_menores_notas</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -25666,7 +25666,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E361" t="n">
@@ -25721,7 +25721,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>39436_human_low</t>
+          <t>39436_humano_menores_notas</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -25736,7 +25736,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E362" t="n">
@@ -25791,7 +25791,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>39446_human_low</t>
+          <t>39446_humano_menores_notas</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -25806,7 +25806,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E363" t="n">
@@ -25861,7 +25861,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>39465_human_high</t>
+          <t>39465_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -25876,7 +25876,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E364" t="n">
@@ -25931,7 +25931,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>39493_human_low</t>
+          <t>39493_humano_menores_notas</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -25946,7 +25946,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E365" t="n">
@@ -26001,7 +26001,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>39502_human_low</t>
+          <t>39502_humano_menores_notas</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -26016,7 +26016,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E366" t="n">
@@ -26071,7 +26071,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>39509_human_high</t>
+          <t>39509_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -26086,7 +26086,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E367" t="n">
@@ -26141,7 +26141,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>39516_human_low</t>
+          <t>39516_humano_menores_notas</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -26156,7 +26156,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E368" t="n">
@@ -26211,7 +26211,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>39561_human_high</t>
+          <t>39561_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -26226,7 +26226,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E369" t="n">
@@ -26281,7 +26281,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>39585_human_high</t>
+          <t>39585_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -26296,7 +26296,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E370" t="n">
@@ -26351,7 +26351,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>39608_human_high</t>
+          <t>39608_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -26366,7 +26366,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E371" t="n">
@@ -26421,7 +26421,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>39614_human_high</t>
+          <t>39614_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -26436,7 +26436,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E372" t="n">
@@ -26491,7 +26491,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>39615_human_low</t>
+          <t>39615_humano_menores_notas</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -26506,7 +26506,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E373" t="n">
@@ -26561,7 +26561,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>39635_human_high</t>
+          <t>39635_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -26576,7 +26576,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E374" t="n">
@@ -26631,7 +26631,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>39648_human_low</t>
+          <t>39648_humano_menores_notas</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -26646,7 +26646,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E375" t="n">
@@ -26701,7 +26701,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>39650_human_high</t>
+          <t>39650_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -26716,7 +26716,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E376" t="n">
@@ -26771,7 +26771,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>39663_human_high</t>
+          <t>39663_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -26786,7 +26786,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E377" t="n">
@@ -26841,7 +26841,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>39684_human_high</t>
+          <t>39684_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -26856,7 +26856,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E378" t="n">
@@ -26911,7 +26911,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>39695_human_low</t>
+          <t>39695_humano_menores_notas</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -26926,7 +26926,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E379" t="n">
@@ -26981,7 +26981,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>39701_human_low</t>
+          <t>39701_humano_menores_notas</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -26996,7 +26996,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E380" t="n">
@@ -27051,7 +27051,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>39715_human_high</t>
+          <t>39715_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -27066,7 +27066,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E381" t="n">
@@ -27121,7 +27121,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>39716_human_high</t>
+          <t>39716_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -27136,7 +27136,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E382" t="n">
@@ -27191,7 +27191,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>39722_human_low</t>
+          <t>39722_humano_menores_notas</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E383" t="n">
@@ -27261,7 +27261,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>39727_human_low</t>
+          <t>39727_humano_menores_notas</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -27276,7 +27276,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E384" t="n">
@@ -27331,7 +27331,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>39786_human_low</t>
+          <t>39786_humano_menores_notas</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -27346,7 +27346,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E385" t="n">
@@ -27401,7 +27401,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>39810_human_high</t>
+          <t>39810_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -27416,7 +27416,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E386" t="n">
@@ -27471,7 +27471,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>39833_human_low</t>
+          <t>39833_humano_menores_notas</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -27486,7 +27486,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E387" t="n">
@@ -27541,7 +27541,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>39896_human_high</t>
+          <t>39896_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -27556,7 +27556,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E388" t="n">
@@ -27611,7 +27611,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>39912_human_low</t>
+          <t>39912_humano_menores_notas</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -27626,7 +27626,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E389" t="n">
@@ -27681,7 +27681,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>39914_human_low</t>
+          <t>39914_humano_menores_notas</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -27696,7 +27696,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E390" t="n">
@@ -27751,7 +27751,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>39956_human_low</t>
+          <t>39956_humano_menores_notas</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -27766,7 +27766,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E391" t="n">
@@ -27821,7 +27821,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>39985_human_low</t>
+          <t>39985_humano_menores_notas</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -27836,7 +27836,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E392" t="n">
@@ -27891,7 +27891,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>39989_human_high</t>
+          <t>39989_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -27906,7 +27906,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E393" t="n">
@@ -27961,7 +27961,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>40004_human_high</t>
+          <t>40004_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -27976,7 +27976,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E394" t="n">
@@ -28031,7 +28031,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>40013_human_high</t>
+          <t>40013_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -28046,7 +28046,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E395" t="n">
@@ -28101,7 +28101,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>40021_human_high</t>
+          <t>40021_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -28116,7 +28116,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E396" t="n">
@@ -28171,7 +28171,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>40024_human_high</t>
+          <t>40024_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -28186,7 +28186,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E397" t="n">
@@ -28241,7 +28241,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>40060_human_high</t>
+          <t>40060_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -28256,7 +28256,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E398" t="n">
@@ -28311,7 +28311,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>40126_human_low</t>
+          <t>40126_humano_menores_notas</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -28326,7 +28326,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E399" t="n">
@@ -28381,7 +28381,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>40127_human_high</t>
+          <t>40127_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -28396,7 +28396,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E400" t="n">
@@ -28451,7 +28451,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>40130_human_high</t>
+          <t>40130_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -28466,7 +28466,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E401" t="n">
@@ -28521,7 +28521,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>40134_human_high</t>
+          <t>40134_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -28536,7 +28536,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E402" t="n">
@@ -28591,7 +28591,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>40140_human_high</t>
+          <t>40140_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -28606,7 +28606,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E403" t="n">
@@ -28661,7 +28661,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>40173_human_high</t>
+          <t>40173_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -28676,7 +28676,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E404" t="n">
@@ -28731,7 +28731,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>40256_human_low</t>
+          <t>40256_humano_menores_notas</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -28746,7 +28746,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E405" t="n">
@@ -28801,7 +28801,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>40270_human_low</t>
+          <t>40270_humano_menores_notas</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -28816,7 +28816,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E406" t="n">
@@ -28871,7 +28871,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>40286_human_high</t>
+          <t>40286_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -28886,7 +28886,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E407" t="n">
@@ -28941,7 +28941,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>40289_human_high</t>
+          <t>40289_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -28956,7 +28956,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E408" t="n">
@@ -29011,7 +29011,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>40297_human_high</t>
+          <t>40297_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -29026,7 +29026,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E409" t="n">
@@ -29081,7 +29081,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>40362_human_low</t>
+          <t>40362_humano_menores_notas</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -29096,7 +29096,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E410" t="n">
@@ -29151,7 +29151,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>40368_human_low</t>
+          <t>40368_humano_menores_notas</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -29166,7 +29166,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E411" t="n">
@@ -29221,7 +29221,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>40426_human_low</t>
+          <t>40426_humano_menores_notas</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -29236,7 +29236,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E412" t="n">
@@ -29291,7 +29291,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>40429_human_high</t>
+          <t>40429_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -29306,7 +29306,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E413" t="n">
@@ -29361,7 +29361,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>40449_human_high</t>
+          <t>40449_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -29376,7 +29376,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E414" t="n">
@@ -29431,7 +29431,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>40461_human_low</t>
+          <t>40461_humano_menores_notas</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -29446,7 +29446,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E415" t="n">
@@ -29501,7 +29501,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>40496_human_low</t>
+          <t>40496_humano_menores_notas</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E416" t="n">
@@ -29571,7 +29571,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>40523_human_low</t>
+          <t>40523_humano_menores_notas</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -29586,7 +29586,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E417" t="n">
@@ -29641,7 +29641,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>40548_human_high</t>
+          <t>40548_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -29656,7 +29656,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E418" t="n">
@@ -29711,7 +29711,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>40580_human_high</t>
+          <t>40580_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -29726,7 +29726,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E419" t="n">
@@ -29781,7 +29781,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>40615_human_high</t>
+          <t>40615_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -29796,7 +29796,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E420" t="n">
@@ -29851,7 +29851,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>40617_human_low</t>
+          <t>40617_humano_menores_notas</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -29866,7 +29866,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E421" t="n">
@@ -29921,7 +29921,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>40621_human_high</t>
+          <t>40621_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -29936,7 +29936,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E422" t="n">
@@ -29991,7 +29991,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>40663_human_high</t>
+          <t>40663_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -30006,7 +30006,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E423" t="n">
@@ -30061,7 +30061,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>40676_human_high</t>
+          <t>40676_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -30076,7 +30076,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E424" t="n">
@@ -30131,7 +30131,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>40688_human_low</t>
+          <t>40688_humano_menores_notas</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -30146,7 +30146,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E425" t="n">
@@ -30201,7 +30201,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>40690_human_low</t>
+          <t>40690_humano_menores_notas</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -30216,7 +30216,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E426" t="n">
@@ -30271,7 +30271,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>40697_human_high</t>
+          <t>40697_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -30286,7 +30286,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E427" t="n">
@@ -30341,7 +30341,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>40710_human_high</t>
+          <t>40710_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -30356,7 +30356,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E428" t="n">
@@ -30411,7 +30411,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>40713_human_high</t>
+          <t>40713_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -30426,7 +30426,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E429" t="n">
@@ -30481,7 +30481,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>40765_human_low</t>
+          <t>40765_humano_menores_notas</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -30496,7 +30496,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E430" t="n">
@@ -30551,7 +30551,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>40772_human_high</t>
+          <t>40772_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -30566,7 +30566,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E431" t="n">
@@ -30621,7 +30621,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>40803_human_low</t>
+          <t>40803_humano_menores_notas</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -30636,7 +30636,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E432" t="n">
@@ -30691,7 +30691,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>40865_human_low</t>
+          <t>40865_humano_menores_notas</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -30706,7 +30706,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E433" t="n">
@@ -30761,7 +30761,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>40869_human_low</t>
+          <t>40869_humano_menores_notas</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -30776,7 +30776,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E434" t="n">
@@ -30831,7 +30831,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>40887_human_low</t>
+          <t>40887_humano_menores_notas</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -30846,7 +30846,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E435" t="n">
@@ -30901,7 +30901,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>40898_human_low</t>
+          <t>40898_humano_menores_notas</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -30916,7 +30916,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E436" t="n">
@@ -30971,7 +30971,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>40906_human_low</t>
+          <t>40906_humano_menores_notas</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -30986,7 +30986,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E437" t="n">
@@ -31041,7 +31041,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>40926_human_low</t>
+          <t>40926_humano_menores_notas</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -31056,7 +31056,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E438" t="n">
@@ -31111,7 +31111,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>40929_human_low</t>
+          <t>40929_humano_menores_notas</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -31126,7 +31126,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E439" t="n">
@@ -31181,7 +31181,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>40943_human_high</t>
+          <t>40943_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -31196,7 +31196,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E440" t="n">
@@ -31251,7 +31251,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>40975_human_high</t>
+          <t>40975_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -31266,7 +31266,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E441" t="n">
@@ -31321,7 +31321,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>40978_human_low</t>
+          <t>40978_humano_menores_notas</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -31336,7 +31336,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E442" t="n">
@@ -31391,7 +31391,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>41011_human_low</t>
+          <t>41011_humano_menores_notas</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -31406,7 +31406,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E443" t="n">
@@ -31461,7 +31461,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>41022_human_high</t>
+          <t>41022_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -31476,7 +31476,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E444" t="n">
@@ -31531,7 +31531,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>41023_human_high</t>
+          <t>41023_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -31546,7 +31546,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E445" t="n">
@@ -31601,7 +31601,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>41088_human_high</t>
+          <t>41088_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -31616,7 +31616,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E446" t="n">
@@ -31671,7 +31671,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>41093_human_low</t>
+          <t>41093_humano_menores_notas</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -31686,7 +31686,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E447" t="n">
@@ -31741,7 +31741,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>41096_human_low</t>
+          <t>41096_humano_menores_notas</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -31756,7 +31756,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E448" t="n">
@@ -31811,7 +31811,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>45015_human_high</t>
+          <t>45015_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -31826,7 +31826,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E449" t="n">
@@ -31881,7 +31881,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>45044_human_low</t>
+          <t>45044_humano_menores_notas</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -31896,7 +31896,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E450" t="n">
@@ -31951,7 +31951,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>45059_human_high</t>
+          <t>45059_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -31966,7 +31966,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E451" t="n">
@@ -32021,7 +32021,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>45075_human_low</t>
+          <t>45075_humano_menores_notas</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -32036,7 +32036,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E452" t="n">
@@ -32091,7 +32091,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>45078_human_low</t>
+          <t>45078_humano_menores_notas</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -32106,7 +32106,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E453" t="n">
@@ -32161,7 +32161,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>45081_human_high</t>
+          <t>45081_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -32176,7 +32176,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E454" t="n">
@@ -32231,7 +32231,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>45124_human_low</t>
+          <t>45124_humano_menores_notas</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -32246,7 +32246,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E455" t="n">
@@ -32301,7 +32301,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>45141_human_high</t>
+          <t>45141_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -32316,7 +32316,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E456" t="n">
@@ -32371,7 +32371,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>45169_human_high</t>
+          <t>45169_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -32386,7 +32386,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E457" t="n">
@@ -32441,7 +32441,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>45186_human_high</t>
+          <t>45186_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -32456,7 +32456,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E458" t="n">
@@ -32511,7 +32511,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>45241_human_low</t>
+          <t>45241_humano_menores_notas</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -32526,7 +32526,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E459" t="n">
@@ -32581,7 +32581,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>45268_human_low</t>
+          <t>45268_humano_menores_notas</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -32596,7 +32596,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E460" t="n">
@@ -32651,7 +32651,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>45279_human_high</t>
+          <t>45279_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -32666,7 +32666,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E461" t="n">
@@ -32721,7 +32721,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>45355_human_high</t>
+          <t>45355_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -32736,7 +32736,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E462" t="n">
@@ -32791,7 +32791,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>45357_human_low</t>
+          <t>45357_humano_menores_notas</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -32806,7 +32806,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E463" t="n">
@@ -32861,7 +32861,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>45389_human_low</t>
+          <t>45389_humano_menores_notas</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -32876,7 +32876,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E464" t="n">
@@ -32931,7 +32931,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>45519_human_low</t>
+          <t>45519_humano_menores_notas</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -32946,7 +32946,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E465" t="n">
@@ -33001,7 +33001,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>45531_human_low</t>
+          <t>45531_humano_menores_notas</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -33016,7 +33016,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E466" t="n">
@@ -33071,7 +33071,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>45576_human_high</t>
+          <t>45576_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -33086,7 +33086,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E467" t="n">
@@ -33141,7 +33141,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>45638_human_low</t>
+          <t>45638_humano_menores_notas</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -33156,7 +33156,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E468" t="n">
@@ -33211,7 +33211,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>45667_human_low</t>
+          <t>45667_humano_menores_notas</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -33226,7 +33226,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E469" t="n">
@@ -33281,7 +33281,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>45746_human_low</t>
+          <t>45746_humano_menores_notas</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -33296,7 +33296,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E470" t="n">
@@ -33351,7 +33351,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>45996_human_low</t>
+          <t>45996_humano_menores_notas</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -33366,7 +33366,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E471" t="n">
@@ -33421,7 +33421,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>46003_human_high</t>
+          <t>46003_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -33436,7 +33436,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E472" t="n">
@@ -33491,7 +33491,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>46034_human_low</t>
+          <t>46034_humano_menores_notas</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -33506,7 +33506,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E473" t="n">
@@ -33561,7 +33561,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>46108_human_low</t>
+          <t>46108_humano_menores_notas</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -33576,7 +33576,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E474" t="n">
@@ -33631,7 +33631,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>46249_human_low</t>
+          <t>46249_humano_menores_notas</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -33646,7 +33646,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E475" t="n">
@@ -33701,7 +33701,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>46255_human_low</t>
+          <t>46255_humano_menores_notas</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -33716,7 +33716,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E476" t="n">
@@ -33771,7 +33771,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>46260_human_high</t>
+          <t>46260_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -33786,7 +33786,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E477" t="n">
@@ -33841,7 +33841,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>46273_human_low</t>
+          <t>46273_humano_menores_notas</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -33856,7 +33856,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E478" t="n">
@@ -33911,7 +33911,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>46276_human_low</t>
+          <t>46276_humano_menores_notas</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -33926,7 +33926,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E479" t="n">
@@ -33981,7 +33981,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>46288_human_low</t>
+          <t>46288_humano_menores_notas</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -33996,7 +33996,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E480" t="n">
@@ -34051,7 +34051,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>46290_human_low</t>
+          <t>46290_humano_menores_notas</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -34066,7 +34066,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E481" t="n">
@@ -34121,7 +34121,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>46321_human_high</t>
+          <t>46321_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -34136,7 +34136,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E482" t="n">
@@ -34191,7 +34191,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>46479_human_high</t>
+          <t>46479_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -34206,7 +34206,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E483" t="n">
@@ -34261,7 +34261,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>46597_human_high</t>
+          <t>46597_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -34276,7 +34276,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E484" t="n">
@@ -34331,7 +34331,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>46626_human_low</t>
+          <t>46626_humano_menores_notas</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -34346,7 +34346,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E485" t="n">
@@ -34401,7 +34401,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>46656_human_high</t>
+          <t>46656_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -34416,7 +34416,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E486" t="n">
@@ -34471,7 +34471,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>46687_human_low</t>
+          <t>46687_humano_menores_notas</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -34486,7 +34486,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E487" t="n">
@@ -34541,7 +34541,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>46699_human_low</t>
+          <t>46699_humano_menores_notas</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -34556,7 +34556,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E488" t="n">
@@ -34611,7 +34611,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>46705_human_low</t>
+          <t>46705_humano_menores_notas</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -34626,7 +34626,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E489" t="n">
@@ -34681,7 +34681,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>46711_human_high</t>
+          <t>46711_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -34696,7 +34696,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E490" t="n">
@@ -34751,7 +34751,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>46724_human_low</t>
+          <t>46724_humano_menores_notas</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -34766,7 +34766,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E491" t="n">
@@ -34821,7 +34821,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>46743_human_low</t>
+          <t>46743_humano_menores_notas</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -34836,7 +34836,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E492" t="n">
@@ -34891,7 +34891,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>46771_human_high</t>
+          <t>46771_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -34906,7 +34906,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E493" t="n">
@@ -34961,7 +34961,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>46946_human_low</t>
+          <t>46946_humano_menores_notas</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -34976,7 +34976,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E494" t="n">
@@ -35031,7 +35031,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>46998_human_high</t>
+          <t>46998_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -35046,7 +35046,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E495" t="n">
@@ -35101,7 +35101,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>47002_human_high</t>
+          <t>47002_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -35116,7 +35116,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E496" t="n">
@@ -35171,7 +35171,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>47010_human_low</t>
+          <t>47010_humano_menores_notas</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -35186,7 +35186,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E497" t="n">
@@ -35241,7 +35241,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>47046_human_low</t>
+          <t>47046_humano_menores_notas</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -35256,7 +35256,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E498" t="n">
@@ -35311,7 +35311,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>47068_human_low</t>
+          <t>47068_humano_menores_notas</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -35326,7 +35326,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E499" t="n">
@@ -35381,7 +35381,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>47099_human_high</t>
+          <t>47099_humano_maiores_notas</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -35396,7 +35396,7 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>human_high</t>
+          <t>humano_maiores_notas</t>
         </is>
       </c>
       <c r="E500" t="n">
@@ -35451,7 +35451,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>47123_human_low</t>
+          <t>47123_humano_menores_notas</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -35466,7 +35466,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>human_low</t>
+          <t>humano_menores_notas</t>
         </is>
       </c>
       <c r="E501" t="n">

--- a/cl_st1_ph3_ednalvo/avaliacao_composicoes/comparacao_de_avaliadores.xlsx
+++ b/cl_st1_ph3_ednalvo/avaliacao_composicoes/comparacao_de_avaliadores.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>adequacao_a_coletanea_human</t>
+          <t>adequacao_a_coletanea_humano</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>adequacao_a_norma_padrao_human</t>
+          <t>adequacao_a_norma_padrao_humano</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -464,7 +464,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>adequacao_ao_tema_human</t>
+          <t>adequacao_ao_tema_humano</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>adequacao_ao_tipo_de_texto_human</t>
+          <t>adequacao_ao_tipo_de_texto_humano</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>coerencia_human</t>
+          <t>coerencia_humano</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>coesao_human</t>
+          <t>coesao_humano</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
@@ -504,12 +504,12 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>pontuacao_total_human</t>
+          <t>pontuacao_total_humano</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>total_diff_ai_minus_human</t>
+          <t>total_diff_ai_minus_humano</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -12781,7 +12781,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -13411,7 +13411,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -13621,7 +13621,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -14041,7 +14041,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -15021,7 +15021,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -15231,7 +15231,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -15511,7 +15511,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -15581,7 +15581,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -15861,7 +15861,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -15931,7 +15931,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -16001,7 +16001,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -16071,7 +16071,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -16281,7 +16281,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -16421,7 +16421,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -16561,7 +16561,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -16631,7 +16631,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -16701,7 +16701,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -16911,7 +16911,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -16981,7 +16981,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -17051,7 +17051,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -17121,7 +17121,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -17261,7 +17261,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -17331,7 +17331,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -17401,7 +17401,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -17471,7 +17471,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -17541,7 +17541,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -17681,7 +17681,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -17821,7 +17821,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -18031,7 +18031,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -18101,7 +18101,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -18171,7 +18171,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -18241,7 +18241,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -18311,7 +18311,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -18381,7 +18381,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -18521,7 +18521,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -18591,7 +18591,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -18661,7 +18661,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -18801,7 +18801,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -18871,7 +18871,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -19011,7 +19011,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -19081,7 +19081,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -19151,7 +19151,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -19361,7 +19361,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -19431,7 +19431,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -19571,7 +19571,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -19711,7 +19711,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -19781,7 +19781,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -19851,7 +19851,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -19921,7 +19921,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -20131,7 +20131,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -20201,7 +20201,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -20271,7 +20271,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -20341,7 +20341,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -20411,7 +20411,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -20481,7 +20481,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -20551,7 +20551,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -20621,7 +20621,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -20691,7 +20691,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -20831,7 +20831,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -20901,7 +20901,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -21041,7 +21041,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -21181,7 +21181,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -21251,7 +21251,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -21321,7 +21321,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -21391,7 +21391,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -21461,7 +21461,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -21601,7 +21601,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -21671,7 +21671,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -21741,7 +21741,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -21811,7 +21811,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -21881,7 +21881,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -21951,7 +21951,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -22231,7 +22231,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -22301,7 +22301,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -22371,7 +22371,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -22441,7 +22441,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -22511,7 +22511,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -22581,7 +22581,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -22651,7 +22651,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -22791,7 +22791,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -22861,7 +22861,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -22931,7 +22931,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -23001,7 +23001,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -23071,7 +23071,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -23141,7 +23141,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -23281,7 +23281,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -23421,7 +23421,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -23561,7 +23561,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -23631,7 +23631,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -23701,7 +23701,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -23771,7 +23771,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -23841,7 +23841,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -23911,7 +23911,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -23981,7 +23981,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -24051,7 +24051,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -24121,7 +24121,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -24191,7 +24191,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -24261,7 +24261,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -24331,7 +24331,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -24401,7 +24401,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -24471,7 +24471,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -24541,7 +24541,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -24611,7 +24611,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -24681,7 +24681,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -24751,7 +24751,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -24821,7 +24821,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -24891,7 +24891,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -24961,7 +24961,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -25031,7 +25031,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -25101,7 +25101,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -25171,7 +25171,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -25241,7 +25241,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -25311,7 +25311,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -25381,7 +25381,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -25451,7 +25451,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -25591,7 +25591,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -25661,7 +25661,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -25731,7 +25731,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -25801,7 +25801,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -25871,7 +25871,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -25941,7 +25941,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -26011,7 +26011,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -26081,7 +26081,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -26151,7 +26151,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -26361,7 +26361,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -26431,7 +26431,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -26501,7 +26501,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -26571,7 +26571,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -26711,7 +26711,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -26781,7 +26781,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -26851,7 +26851,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -26921,7 +26921,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -26991,7 +26991,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -27061,7 +27061,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -27131,7 +27131,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -27201,7 +27201,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -27271,7 +27271,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -27481,7 +27481,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -27551,7 +27551,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -27621,7 +27621,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -27691,7 +27691,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -27761,7 +27761,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -27831,7 +27831,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -27901,7 +27901,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -27971,7 +27971,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -28041,7 +28041,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -28111,7 +28111,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -28181,7 +28181,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -28251,7 +28251,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -28321,7 +28321,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -28391,7 +28391,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -28461,7 +28461,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -28531,7 +28531,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -28601,7 +28601,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -28671,7 +28671,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -28741,7 +28741,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -28811,7 +28811,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -28881,7 +28881,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -28951,7 +28951,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -29021,7 +29021,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -29091,7 +29091,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -29161,7 +29161,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -29231,7 +29231,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -29301,7 +29301,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -29371,7 +29371,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -29441,7 +29441,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -29511,7 +29511,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -29581,7 +29581,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -29651,7 +29651,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -29721,7 +29721,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -29791,7 +29791,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -29861,7 +29861,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -29931,7 +29931,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -30001,7 +30001,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -30071,7 +30071,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -30141,7 +30141,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -30211,7 +30211,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -30281,7 +30281,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -30351,7 +30351,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -30421,7 +30421,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -30491,7 +30491,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -30631,7 +30631,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -30701,7 +30701,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -30771,7 +30771,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -30841,7 +30841,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -30911,7 +30911,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -30981,7 +30981,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -31051,7 +31051,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -31121,7 +31121,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -31191,7 +31191,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -31261,7 +31261,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -31331,7 +31331,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -31401,7 +31401,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -31471,7 +31471,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -31541,7 +31541,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -31611,7 +31611,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -31681,7 +31681,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -31751,7 +31751,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -31891,7 +31891,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -31961,7 +31961,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -32031,7 +32031,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -32101,7 +32101,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -32171,7 +32171,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -32241,7 +32241,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -32311,7 +32311,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -32381,7 +32381,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -32451,7 +32451,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -32521,7 +32521,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -32591,7 +32591,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -32661,7 +32661,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -32731,7 +32731,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -32801,7 +32801,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -32871,7 +32871,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -32941,7 +32941,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -33011,7 +33011,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -33081,7 +33081,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -33151,7 +33151,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -33221,7 +33221,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -33291,7 +33291,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -33361,7 +33361,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -33431,7 +33431,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -33501,7 +33501,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -33571,7 +33571,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -33641,7 +33641,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -33711,7 +33711,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -33781,7 +33781,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -33851,7 +33851,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -33921,7 +33921,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -33991,7 +33991,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -34061,7 +34061,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -34131,7 +34131,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -34201,7 +34201,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -34271,7 +34271,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -34341,7 +34341,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -34411,7 +34411,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -34481,7 +34481,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -34551,7 +34551,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -34621,7 +34621,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -34691,7 +34691,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -34761,7 +34761,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -34831,7 +34831,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -34901,7 +34901,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -34971,7 +34971,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -35041,7 +35041,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -35111,7 +35111,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -35181,7 +35181,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -35251,7 +35251,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -35321,7 +35321,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -35391,7 +35391,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>maiores_notas</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -35461,7 +35461,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>menores_notas</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
